--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484258_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484258_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9638</v>
+        <v>3.246</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4005</v>
+        <v>1.7643</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5633</v>
+        <v>1.4816</v>
       </c>
       <c r="G2" t="n">
         <v>3.9627</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0353</v>
+        <v>0.2469</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5831</v>
+        <v>-0.2192</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5478</v>
+        <v>0.4661</v>
       </c>
       <c r="V2" t="n">
         <v>1.1851</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9331</v>
+        <v>2.0443</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4729</v>
+        <v>1.2301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4602</v>
+        <v>0.8142</v>
       </c>
       <c r="G3" t="n">
         <v>1.0749</v>
@@ -688,13 +688,13 @@
         <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1233</v>
+        <v>0.2346</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4625</v>
+        <v>0.2197</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3391</v>
+        <v>0.0149</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2186</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2436</v>
+        <v>-1.3985</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6113</v>
+        <v>-0.4568</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3677</v>
+        <v>-0.9417</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9177</v>
+        <v>-0.3688</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9568</v>
+        <v>-0.8138</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0391</v>
+        <v>0.4449</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9765</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0169</v>
+        <v>-0.6741</v>
       </c>
       <c r="L4" t="n">
         <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0587</v>
+        <v>0.2648</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0601</v>
+        <v>-0.1397</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0014</v>
+        <v>0.4045</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4367</v>
+        <v>-0.1431</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9552</v>
+        <v>-0.1004</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4816</v>
+        <v>-0.0427</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.0801</v>
+        <v>-0.8865</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0801</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7369</v>
+        <v>-2.7708</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.659</v>
+        <v>-1.6132</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0778</v>
+        <v>-1.1575</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3688</v>
+        <v>-0.9177</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8138</v>
+        <v>-0.9568</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4449</v>
+        <v>0.0391</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.9765</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6741</v>
+        <v>-1.0169</v>
       </c>
       <c r="L5" t="n">
         <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2648</v>
+        <v>0.0587</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1397</v>
+        <v>0.0601</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4045</v>
+        <v>-0.0014</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4815</v>
+        <v>1.4224</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>0.7307</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1789</v>
+        <v>0.6917</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8865</v>
+        <v>-3.0801</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1638</v>
+        <v>-3.0801</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2828</v>
+        <v>-2.8447</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9835</v>
+        <v>-1.3275</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2993</v>
+        <v>-1.5172</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2018</v>
@@ -922,13 +922,13 @@
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0242</v>
+        <v>-0.586</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3331</v>
+        <v>-0.0108</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3573</v>
+        <v>-0.5752</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8615</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.0237</v>
+        <v>-3.4653</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.2682</v>
+        <v>-3.681</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2445</v>
+        <v>0.2157</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4869</v>
+        <v>-3.8895</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7066</v>
+        <v>-1.2456</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7803</v>
+        <v>-2.6439</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0067</v>
+        <v>-2.655</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6319</v>
+        <v>-0.6869</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3748</v>
+        <v>-1.968</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4801</v>
+        <v>-1.2346</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0747</v>
+        <v>-0.5587</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4054</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-1.3674</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0.7546</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1127</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6428</v>
+        <v>0.6904</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.307</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5842</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1246</v>
+        <v>-3.7532</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4493</v>
+        <v>-4.1066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3246</v>
+        <v>0.3534</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8895</v>
+        <v>-2.4869</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2456</v>
+        <v>-0.7066</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6439</v>
+        <v>-1.7803</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.655</v>
+        <v>-2.0067</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6869</v>
+        <v>-0.6319</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.968</v>
+        <v>-1.3748</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2346</v>
+        <v>-0.4801</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5587</v>
+        <v>-0.0747</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4054</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3674</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.4849</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.0489</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7993</v>
+        <v>-0.5339</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.307</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9369</v>
+        <v>-4.1457</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1578</v>
+        <v>-4.8515</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.779</v>
+        <v>0.7058</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3909</v>
+        <v>-3.78</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8138</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.594</v>
+        <v>-2.9662</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2455</v>
+        <v>-3.624</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6524</v>
+        <v>-0.7944</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.8296</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1453</v>
+        <v>-0.156</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1445</v>
+        <v>-0.0194</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0008</v>
+        <v>-0.1366</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3441</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4874</v>
+        <v>-1.0083</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.528</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7006</v>
+        <v>-0.4803</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8865</v>
+        <v>-0.9201</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1052</v>
+        <v>-1.1973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9854</v>
+        <v>-4.5596</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0649</v>
+        <v>-2.7534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0794</v>
+        <v>-1.8063</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.78</v>
+        <v>-1.3909</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8138</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9662</v>
+        <v>-0.594</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.624</v>
+        <v>-1.2455</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7944</v>
+        <v>-0.6524</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8296</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.156</v>
+        <v>-0.1453</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0194</v>
+        <v>-0.1445</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1366</v>
+        <v>-0.0008</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-2.3441</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.8481</v>
+        <v>-1.1102</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7414</v>
+        <v>-0.3823</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1067</v>
+        <v>-0.7278</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9201</v>
+        <v>-0.8865</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1973</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.9498</v>
+        <v>-17.6475</v>
       </c>
       <c r="E11" t="n">
-        <v>-16.098</v>
+        <v>-15.7956</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8518</v>
+        <v>-1.852</v>
       </c>
       <c r="G11" t="n">
         <v>-7.998000000000001</v>
@@ -1282,16 +1282,16 @@
         <v>-1.2511</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.7469</v>
+        <v>-6.746899999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.146100000000001</v>
+        <v>-4.1461</v>
       </c>
       <c r="K11" t="n">
         <v>1.2418</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.3877</v>
+        <v>-5.387699999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-3.8519</v>
@@ -1312,13 +1312,13 @@
         <v>15.6275</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9768000000000003</v>
+        <v>-0.6739999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4799</v>
+        <v>-0.1772</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4967000000000001</v>
+        <v>-0.4967999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-8.975199999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.3217</v>
+        <v>10.1994</v>
       </c>
       <c r="E12" t="n">
-        <v>7.5478</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7739</v>
+        <v>2.0449</v>
       </c>
       <c r="G12" t="n">
         <v>4.7414</v>
@@ -1390,13 +1390,13 @@
         <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4114</v>
+        <v>-0.5337</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.96</v>
+        <v>-0.3533</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4514</v>
+        <v>-0.1804</v>
       </c>
       <c r="V12" t="n">
         <v>4.8197</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9812</v>
+        <v>6.5943</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6862</v>
+        <v>2.1917</v>
       </c>
       <c r="F13" t="n">
-        <v>4.295</v>
+        <v>4.4026</v>
       </c>
       <c r="G13" t="n">
         <v>3.5409</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7198</v>
+        <v>-0.1066</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.96</v>
+        <v>-0.4544</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2402</v>
+        <v>0.3478</v>
       </c>
       <c r="V13" t="n">
         <v>2.7693</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2735</v>
+        <v>5.0247</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2265</v>
+        <v>2.9231</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0471</v>
+        <v>2.1015</v>
       </c>
       <c r="G14" t="n">
         <v>0.6798999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8123</v>
+        <v>0.5634</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4487</v>
+        <v>0.1454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3636</v>
+        <v>0.418</v>
       </c>
       <c r="V14" t="n">
         <v>1.8279</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8065</v>
+        <v>3.1288</v>
       </c>
       <c r="E15" t="n">
-        <v>0.738</v>
+        <v>-0.4754</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0685</v>
+        <v>3.6041</v>
       </c>
       <c r="G15" t="n">
         <v>1.3994</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2899</v>
+        <v>1.6122</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2206</v>
+        <v>1.0072</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0694</v>
+        <v>0.605</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8003</v>
+        <v>2.1469</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2061</v>
+        <v>1.4983</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5942</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.6854</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1149</v>
+        <v>0.4615</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0456</v>
+        <v>0.3378</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0693</v>
+        <v>0.1238</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8673</v>
+        <v>-0.0118</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3364</v>
+        <v>-2.0754</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5308</v>
+        <v>2.0636</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3737</v>
+        <v>0.2096</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.549</v>
+        <v>0.5874</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1753</v>
+        <v>-0.3778</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0405</v>
+        <v>-0.4496</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.7368</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-1.1863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4142</v>
+        <v>0.6591</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.549</v>
+        <v>-0.1494</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>0.8085</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2982</v>
+        <v>0.3962</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>0.1638</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1167</v>
+        <v>0.2324</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2681</v>
+        <v>-0.7389</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0865</v>
+        <v>-0.2353</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8185</v>
+        <v>-0.5036</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2096</v>
+        <v>-0.3737</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5874</v>
+        <v>-0.549</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3778</v>
+        <v>0.1753</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4496</v>
+        <v>0.0405</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7368</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1863</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6591</v>
+        <v>-0.4142</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1494</v>
+        <v>-0.549</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8085</v>
+        <v>0.1348</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8601</v>
+        <v>-0.1699</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0127</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9738</v>
+        <v>-1.8195</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7146</v>
+        <v>-3.6135</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7408</v>
+        <v>1.7939</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7569</v>
@@ -1936,13 +1936,13 @@
         <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.6486</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4758</v>
+        <v>-0.3747</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.327</v>
+        <v>-0.2739</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.1242</v>
+        <v>-5.8998</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.415</v>
+        <v>-6.5162</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2909</v>
+        <v>0.6163</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1279</v>
@@ -2014,13 +2014,13 @@
         <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.148</v>
+        <v>0.0764</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2066</v>
+        <v>0.1055</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3546</v>
+        <v>-0.0291</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3321</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>17.9498</v>
+        <v>18.6241</v>
       </c>
       <c r="E21" t="n">
-        <v>1.852099999999999</v>
+        <v>1.851799999999998</v>
       </c>
       <c r="F21" t="n">
-        <v>16.0981</v>
+        <v>16.772</v>
       </c>
       <c r="G21" t="n">
         <v>7.998099999999999</v>
@@ -2071,7 +2071,7 @@
         <v>2.4929</v>
       </c>
       <c r="L21" t="n">
-        <v>1.359300000000001</v>
+        <v>1.359300000000002</v>
       </c>
       <c r="M21" t="n">
         <v>4.146199999999999</v>
@@ -2092,13 +2092,13 @@
         <v>15.6275</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9767000000000002</v>
+        <v>1.6509</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4968000000000002</v>
+        <v>0.4968</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4800999999999997</v>
+        <v>1.1542</v>
       </c>
       <c r="V21" t="n">
         <v>8.975100000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484258_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484258_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.6428</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +736,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3985</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4568</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9417</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3688</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8138</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4449</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1397</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -766,28 +781,33 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1431</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1004</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0427</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.7708</v>
+        <v>-1.3985</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6132</v>
+        <v>-0.4568</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1575</v>
+        <v>-0.9417</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9177</v>
+        <v>-0.3688</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9568</v>
+        <v>-0.8138</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0391</v>
+        <v>0.4449</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9765</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0169</v>
+        <v>-0.6741</v>
       </c>
       <c r="L5" t="n">
         <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0587</v>
+        <v>0.2648</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0601</v>
+        <v>-0.1397</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0014</v>
+        <v>0.4045</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4224</v>
+        <v>-0.1431</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7307</v>
+        <v>-0.1004</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6917</v>
+        <v>-0.0427</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.0801</v>
+        <v>-0.8865</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.0801</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8447</v>
+        <v>-2.7708</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3275</v>
+        <v>-1.6132</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5172</v>
+        <v>-1.1575</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2018</v>
+        <v>-0.9177</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8501</v>
+        <v>-0.9568</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0519</v>
+        <v>0.0391</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8321</v>
+        <v>-0.9765</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4786</v>
+        <v>-1.0169</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6465</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.034</v>
+        <v>0.0587</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4054</v>
+        <v>-0.0014</v>
       </c>
       <c r="P6" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>-1.3674</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.586</v>
+        <v>1.4224</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0108</v>
+        <v>0.7307</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5752</v>
+        <v>0.6917</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8615</v>
+        <v>-3.0801</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8615</v>
+        <v>-3.0801</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +985,72 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4653</v>
+        <v>-2.8447</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.681</v>
+        <v>-1.3275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2157</v>
+        <v>-1.5172</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8895</v>
+        <v>-0.2018</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2456</v>
+        <v>0.8501</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6439</v>
+        <v>-1.0519</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.655</v>
+        <v>0.8321</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6869</v>
+        <v>1.4786</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.968</v>
+        <v>-0.6465</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2346</v>
+        <v>-1.034</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5587</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4054</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3674</v>
+        <v>-2.1488</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7546</v>
+        <v>-0.586</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6904</v>
+        <v>-0.5752</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.307</v>
+        <v>-1.8615</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5842</v>
+        <v>-1.8615</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1457</v>
+        <v>-4.0722</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8515</v>
+        <v>-4.2879</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7058</v>
+        <v>0.2157</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.78</v>
+        <v>-4.4965</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8138</v>
+        <v>-1.2456</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9662</v>
+        <v>-3.2509</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.624</v>
+        <v>-3.262</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7944</v>
+        <v>-0.6869</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.8296</v>
+        <v>-2.575</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.156</v>
+        <v>-1.2346</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0194</v>
+        <v>-0.5587</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1366</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0083</v>
+        <v>0.7546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.528</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4803</v>
+        <v>0.6904</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9201</v>
+        <v>-1.307</v>
       </c>
       <c r="W9" t="n">
         <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1973</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5596</v>
+        <v>-4.1457</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7534</v>
+        <v>-4.8515</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8063</v>
+        <v>0.7058</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3909</v>
+        <v>-3.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8138</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.594</v>
+        <v>-2.9662</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2455</v>
+        <v>-3.624</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6524</v>
+        <v>-0.7944</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.8296</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1453</v>
+        <v>-0.156</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1445</v>
+        <v>-0.0194</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0008</v>
+        <v>-0.1366</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3441</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1102</v>
+        <v>-1.0083</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3823</v>
+        <v>-0.528</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7278</v>
+        <v>-0.4803</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8865</v>
+        <v>-0.9201</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1052</v>
+        <v>-1.1973</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.6475</v>
+        <v>-4.5596</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.7956</v>
+        <v>-2.7534</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.852</v>
+        <v>-1.8063</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.998000000000001</v>
+        <v>-1.3909</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2511</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.746899999999999</v>
+        <v>-0.594</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1461</v>
+        <v>-1.2455</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2418</v>
+        <v>-0.6524</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.387699999999999</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8519</v>
+        <v>-0.1453</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4929</v>
+        <v>-0.1445</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.359</v>
+        <v>-0.0008</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-15.6275</v>
+        <v>-2.3441</v>
       </c>
       <c r="R11" t="n">
-        <v>15.6275</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6739999999999997</v>
+        <v>-1.1102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1772</v>
+        <v>-0.3823</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4967999999999999</v>
+        <v>-0.7278</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.975199999999999</v>
+        <v>-0.8865</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1553</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.1308</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.1994</v>
+        <v>-17.6474</v>
       </c>
       <c r="E12" t="n">
-        <v>8.154500000000001</v>
+        <v>-15.7955</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0449</v>
+        <v>-1.852</v>
       </c>
       <c r="G12" t="n">
-        <v>4.7414</v>
+        <v>-7.998000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8296</v>
+        <v>-1.2511</v>
       </c>
       <c r="I12" t="n">
-        <v>5.571</v>
+        <v>-6.746900000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>5.0556</v>
+        <v>-4.146100000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.023</v>
+        <v>1.2418</v>
       </c>
       <c r="L12" t="n">
-        <v>5.0326</v>
+        <v>-5.387700000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3141</v>
+        <v>-3.851900000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8526</v>
+        <v>-2.4929</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5385</v>
+        <v>-1.359</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3674</v>
+        <v>-15.6275</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>15.6275</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5337</v>
+        <v>-0.6739999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3533</v>
+        <v>-0.1772</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1804</v>
+        <v>-0.4968000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8197</v>
+        <v>-8.975199999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>4.8197</v>
+        <v>4.1553</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-13.1308</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5943</v>
+        <v>10.1994</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1917</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4026</v>
+        <v>2.0449</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5409</v>
+        <v>4.7414</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1412</v>
+        <v>-0.8296</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3997</v>
+        <v>5.571</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7484</v>
+        <v>5.0556</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2916</v>
+        <v>0.023</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4568</v>
+        <v>5.0326</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7926</v>
+        <v>-0.3141</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8496</v>
+        <v>-0.8526</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9429</v>
+        <v>0.5385</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-1.3674</v>
       </c>
       <c r="R13" t="n">
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1066</v>
+        <v>-0.5337</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4544</v>
+        <v>-0.3533</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3478</v>
+        <v>-0.1804</v>
       </c>
       <c r="V13" t="n">
-        <v>2.7693</v>
+        <v>4.8197</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0466</v>
+        <v>4.8197</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0247</v>
+        <v>6.5943</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9231</v>
+        <v>2.1917</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1015</v>
+        <v>4.4026</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6798999999999999</v>
+        <v>3.5409</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3039</v>
+        <v>1.1412</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9838</v>
+        <v>2.3997</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2586</v>
+        <v>1.7484</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.2916</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1755</v>
+        <v>1.4568</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5787</v>
+        <v>1.7926</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.387</v>
+        <v>0.8496</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8083</v>
+        <v>0.9429</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="R14" t="n">
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5634</v>
+        <v>-0.1066</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1454</v>
+        <v>-0.4544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.418</v>
+        <v>0.3478</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8279</v>
+        <v>2.7693</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>3.0466</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1288</v>
+        <v>5.0247</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4754</v>
+        <v>2.9231</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6041</v>
+        <v>2.1015</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3994</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4528</v>
+        <v>-1.3039</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0535</v>
+        <v>1.9838</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1422</v>
+        <v>1.2586</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1241</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2663</v>
+        <v>1.1755</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5416</v>
+        <v>-0.5787</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3288</v>
+        <v>-1.387</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2128</v>
+        <v>0.8083</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6122</v>
+        <v>0.5634</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0072</v>
+        <v>0.1454</v>
       </c>
       <c r="U15" t="n">
-        <v>0.605</v>
+        <v>0.418</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8317</v>
+        <v>2.1052</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1469</v>
+        <v>2.5218</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4983</v>
+        <v>-1.0824</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6487000000000001</v>
+        <v>3.6041</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6854</v>
+        <v>0.7924</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0806</v>
+        <v>1.4528</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6048</v>
+        <v>-0.6605</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3558</v>
+        <v>-1.7492</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0205</v>
+        <v>0.1241</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3354</v>
+        <v>-1.8733</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3296</v>
+        <v>2.5416</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0601</v>
+        <v>1.3288</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>1.2128</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4615</v>
+        <v>1.6122</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3378</v>
+        <v>1.0072</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1238</v>
+        <v>0.605</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0118</v>
+        <v>2.1469</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0754</v>
+        <v>1.4983</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0636</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2096</v>
+        <v>1.6854</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5874</v>
+        <v>0.0806</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3778</v>
+        <v>1.6048</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4496</v>
+        <v>1.3558</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7368</v>
+        <v>0.0205</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1863</v>
+        <v>1.3354</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6591</v>
+        <v>0.3296</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1494</v>
+        <v>0.0601</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8085</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3962</v>
+        <v>0.4615</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1638</v>
+        <v>0.3378</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2324</v>
+        <v>0.1238</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7389</v>
+        <v>0.607</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2353</v>
+        <v>0.607</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5036</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3737</v>
+        <v>0.607</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.549</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1753</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4142</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.549</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1699</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0805</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8195</v>
+        <v>-0.0118</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6135</v>
+        <v>-2.0754</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7939</v>
+        <v>2.0636</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7569</v>
+        <v>0.2096</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1973</v>
+        <v>0.5874</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9542</v>
+        <v>-0.3778</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0667</v>
+        <v>-0.4496</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0217</v>
+        <v>0.7368</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0884</v>
+        <v>-1.1863</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3098</v>
+        <v>0.6591</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1755</v>
+        <v>-0.1494</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1342</v>
+        <v>0.8085</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-2.3441</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6486</v>
+        <v>0.3962</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3747</v>
+        <v>0.1638</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2739</v>
+        <v>0.2324</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.8998</v>
+        <v>-0.7389</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.5162</v>
+        <v>-0.2353</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6163</v>
+        <v>-0.5036</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1279</v>
+        <v>-0.3737</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4743</v>
+        <v>-0.549</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6022</v>
+        <v>0.1753</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9484</v>
+        <v>0.0405</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1921</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.1405</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1795</v>
+        <v>-0.4142</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7178</v>
+        <v>-0.549</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5383</v>
+        <v>0.1348</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.5162</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.4463</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0764</v>
+        <v>-0.1699</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1055</v>
+        <v>-0.0805</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0291</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,235 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-1.8195</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.6135</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.7939</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.7569</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1973</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1.9542</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.0667</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.0884</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.6486</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.3747</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.2739</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>J. GASCON TORNE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.8998</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-6.5162</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.1279</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.6022</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.9484</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.1921</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-3.1405</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1795</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7178</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-6.4463</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.7731</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484258_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>18.6241</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>1.851799999999998</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>16.772</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G23" t="n">
         <v>7.998099999999999</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H23" t="n">
         <v>1.2511</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>6.7469</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>3.852</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K23" t="n">
         <v>2.4929</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.359300000000002</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.146199999999999</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="L23" t="n">
+        <v>1.359300000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.1462</v>
+      </c>
+      <c r="N23" t="n">
         <v>-1.2418</v>
       </c>
-      <c r="O21" t="n">
-        <v>5.387700000000001</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="O23" t="n">
+        <v>5.387699999999999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-15.6274</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R23" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>1.6509</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>0.4968</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>1.1542</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V23" t="n">
         <v>8.975100000000001</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>13.1308</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-4.1555</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
